--- a/tests/worked_examples/end_to_end/replacement_and_residual_value.xlsx
+++ b/tests/worked_examples/end_to_end/replacement_and_residual_value.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">A 10,000 EUR device with an 8-year service life over a 12-year horizon at 3 % interest, with investment prices escalating at 2 % per year. The device is replaced once in year 8 at the escalated price; at the end of the horizon 4 of the replacement's 8 years are still unused, so half of the escalated price is credited back as residual value.</t>
+    <t xml:space="preserve">A 10,000 EUR device with an 8-year service life over a 12-year horizon at 3 % interest, with investment prices escalating at 2 % per year. The device is replaced once in year 8 at the escalated price; at the end of the horizon 4 of the replacement's 8 years are still unused, so half of the escalated price is credited back as residual value. The residual is the VDI 2067-1 / DIN EN 15459-1 book value: the last installation's price escalated to its own installation year - never to the horizon - written down straight-line over the service life and discounted from year T. It is deliberately not a market-value estimate.</t>
   </si>
   <si>
     <t xml:space="preserve">reviewed_by</t>
@@ -160,7 +160,7 @@
     <t xml:space="preserve">nominal_residual_value_year_12_in_euro</t>
   </si>
   <si>
-    <t xml:space="preserve">4 of 8 years of the replacement are still unused at the end of the horizon</t>
+    <t xml:space="preserve">4 of 8 years of the replacement are still unused at the end of the horizon. Single-replacement scenario by construction: 2*lifetime_in_years-horizon_in_years is the unused remainder only while lifetime_in_years &lt;= horizon_in_years &lt; 2*lifetime_in_years</t>
   </si>
   <si>
     <t xml:space="preserve">npv_residual_value_in_euro</t>
@@ -258,12 +258,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -470,298 +474,298 @@
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>0.03</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>0.02</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <f aca="false">investment_in_euro*(1+investment_price_escalation_rate)^lifetime_in_years</f>
         <v>11716.5938100227</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="0" t="n">
-        <f aca="false">nominal_replacement_year_8_in_euro/(1+interest_rate)^8</f>
+      <c r="B22" s="1" t="n">
+        <f aca="false">nominal_replacement_year_8_in_euro/(1+interest_rate)^lifetime_in_years</f>
         <v>9249.18734833738</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="3" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="0" t="n">
-        <f aca="false">-nominal_replacement_year_8_in_euro*(lifetime_in_years+8-horizon_in_years)/lifetime_in_years</f>
+      <c r="B23" s="1" t="n">
+        <f aca="false">-nominal_replacement_year_8_in_euro*(2*lifetime_in_years-horizon_in_years)/lifetime_in_years</f>
         <v>-5858.29690501133</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <f aca="false">nominal_residual_value_year_12_in_euro/(1+interest_rate)^horizon_in_years</f>
         <v>-4108.89158137171</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="3" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <f aca="false">investment_in_euro</f>
         <v>10000</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="3" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <f aca="false">npv_investment_in_euro+npv_replacement_in_euro+npv_residual_value_in_euro</f>
         <v>15140.2957669657</v>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="3" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <f aca="false">interest_rate*(1+interest_rate)^horizon_in_years/((1+interest_rate)^horizon_in_years-1)</f>
         <v>0.100462085472963</v>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="3" t="n">
         <v>1E-006</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <f aca="false">total_npv_in_euro*annuity_factor</f>
         <v>1521.02568742684</v>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="3" t="n">
         <v>0.01</v>
       </c>
     </row>
